--- a/survey_templates/046_survey_distribution_timing_questionnaire--survey_templates.xlsx
+++ b/survey_templates/046_survey_distribution_timing_questionnaire--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'email'}</t>
+          <t>email</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'message'}</t>
+          <t>message</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'message'}</t>
+          <t>message</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'text'}</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'text'}</t>
+          <t>text</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'first'}</t>
+          <t>first</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'first'}</t>
+          <t>first</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'second'}</t>
+          <t>second</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'second'}</t>
+          <t>second</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'third'}</t>
+          <t>third</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'third'}</t>
+          <t>third</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'fourth'}</t>
+          <t>fourth</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'fourth'}</t>
+          <t>fourth</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'fifth'}</t>
+          <t>fifth</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'fifth'}</t>
+          <t>fifth</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'one_time'}</t>
+          <t>one_time</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'one_time'}</t>
+          <t>one time</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'minutes'}</t>
+          <t>minutes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'minutes'}</t>
+          <t>minutes</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'hours'}</t>
+          <t>hours</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'hours'}</t>
+          <t>hours</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'days'}</t>
+          <t>days</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'days'}</t>
+          <t>days</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'est'}</t>
+          <t>est</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'EST'}</t>
+          <t>EST</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'pst'}</t>
+          <t>pst</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'PST'}</t>
+          <t>PST</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cst'}</t>
+          <t>cst</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'CST'}</t>
+          <t>CST</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'mst'}</t>
+          <t>mst</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'MST'}</t>
+          <t>MST</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'ast'}</t>
+          <t>ast</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'AST'}</t>
+          <t>AST</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'america'}</t>
+          <t>america</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'America'}</t>
+          <t>America</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'europe'}</t>
+          <t>europe</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Europe'}</t>
+          <t>Europe</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'asia'}</t>
+          <t>asia</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Asia'}</t>
+          <t>Asia</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'africa'}</t>
+          <t>africa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Africa'}</t>
+          <t>Africa</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'australia'}</t>
+          <t>australia</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Australia'}</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_0}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 0}</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_0}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 0}</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_-1}</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': -1}</t>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_-2}</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': -2}</t>
+          <t>-2</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_-3}</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': -3}</t>
+          <t>-3</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_-4}</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': -4}</t>
+          <t>-4</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_0}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 0}</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_-1}</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': -1}</t>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_-2}</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': -2}</t>
+          <t>-2</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_-3}</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': -3}</t>
+          <t>-3</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_-4}</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': -4}</t>
+          <t>-4</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_0}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 0}</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_0}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 0}</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_0}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 0}</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_0}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 0}</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_-1}</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': -1}</t>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_-2}</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': -2}</t>
+          <t>-2</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_-3}</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': -3}</t>
+          <t>-3</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_-4}</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': -4}</t>
+          <t>-4</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_0}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 0}</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_-1}</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': -1}</t>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_-2}</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': -2}</t>
+          <t>-2</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_-3}</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': -3}</t>
+          <t>-3</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_-4}</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': -4}</t>
+          <t>-4</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_0}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 0}</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2423,12 +2423,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2457,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_0}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 0}</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2508,12 +2508,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2525,12 +2525,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_0}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 0}</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2644,12 +2644,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_0}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 0}</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2695,12 +2695,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2712,12 +2712,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2729,12 +2729,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2746,12 +2746,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_0}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 0}</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2763,12 +2763,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2797,12 +2797,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
